--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/oct-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/oct-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC oct-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC oct-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9409,7 +9409,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9642,7 +9642,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9886,7 +9886,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10130,7 +10130,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10313,7 +10313,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10435,7 +10435,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10618,7 +10618,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10740,7 +10740,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10801,7 +10801,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10984,7 +10984,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11167,7 +11167,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11289,7 +11289,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11472,7 +11472,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11655,7 +11655,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11777,7 +11777,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11838,7 +11838,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11960,7 +11960,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12021,7 +12021,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12082,7 +12082,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12143,7 +12143,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12326,7 +12326,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12387,7 +12387,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12448,7 +12448,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12570,7 +12570,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12875,7 +12875,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -12997,7 +12997,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13058,7 +13058,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13180,7 +13180,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13302,7 +13302,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -13363,7 +13363,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13485,7 +13485,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13546,7 +13546,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13607,7 +13607,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13729,7 +13729,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -13790,7 +13790,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13912,7 +13912,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -13973,7 +13973,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14034,7 +14034,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14156,7 +14156,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14217,7 +14217,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -14278,7 +14278,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14339,7 +14339,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14461,7 +14461,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14522,7 +14522,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -14583,7 +14583,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -14827,7 +14827,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -14888,7 +14888,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -14949,7 +14949,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -15010,7 +15010,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15071,7 +15071,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -15132,7 +15132,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -15193,7 +15193,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -15254,7 +15254,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -15315,7 +15315,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -15376,7 +15376,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -15437,7 +15437,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15559,7 +15559,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -15620,7 +15620,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -15742,7 +15742,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -15803,7 +15803,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -15864,7 +15864,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -15925,7 +15925,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -15986,7 +15986,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -16108,7 +16108,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -16169,7 +16169,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -16230,7 +16230,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -16291,7 +16291,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -16352,7 +16352,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -16367,7 +16367,7 @@
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -16417,7 +16417,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -16478,7 +16478,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16539,7 +16539,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -16600,7 +16600,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -16661,7 +16661,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -16722,7 +16722,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -16783,7 +16783,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -16905,7 +16905,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -16966,7 +16966,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -17027,7 +17027,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -17088,7 +17088,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -17149,7 +17149,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -17210,7 +17210,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -17271,7 +17271,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -17332,7 +17332,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -17393,7 +17393,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -17454,7 +17454,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -17515,7 +17515,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -17576,7 +17576,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -17637,7 +17637,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -17698,7 +17698,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -17820,7 +17820,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -17881,7 +17881,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -17942,7 +17942,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -18003,7 +18003,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -18064,7 +18064,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -18125,7 +18125,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -18186,7 +18186,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -18247,7 +18247,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -18308,7 +18308,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -18430,7 +18430,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -18491,7 +18491,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -18552,7 +18552,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -18613,7 +18613,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -18674,7 +18674,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -18735,7 +18735,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -18796,7 +18796,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -18857,7 +18857,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -18918,7 +18918,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -18979,7 +18979,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -19040,7 +19040,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -19101,7 +19101,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -19162,7 +19162,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -19223,7 +19223,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -19284,7 +19284,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -19345,7 +19345,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -19406,7 +19406,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -19467,7 +19467,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -19528,7 +19528,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -19589,7 +19589,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -19650,7 +19650,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -19711,7 +19711,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -19772,7 +19772,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -19833,7 +19833,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -19955,7 +19955,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -20016,7 +20016,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -20077,7 +20077,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -20138,7 +20138,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -20199,7 +20199,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -20260,7 +20260,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -20321,7 +20321,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -20382,7 +20382,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -20504,7 +20504,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -20565,7 +20565,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -20626,7 +20626,7 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -20687,7 +20687,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -20748,7 +20748,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -20870,7 +20870,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -20931,7 +20931,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -21053,7 +21053,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -21236,7 +21236,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -21297,7 +21297,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -21358,7 +21358,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -21419,7 +21419,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -21480,7 +21480,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -21541,7 +21541,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -21602,7 +21602,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -21663,7 +21663,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -21724,7 +21724,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -21785,7 +21785,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -21846,7 +21846,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -21907,7 +21907,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -21968,7 +21968,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -22090,7 +22090,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -22151,7 +22151,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -22212,7 +22212,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -22273,7 +22273,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -22334,7 +22334,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -22395,7 +22395,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -22456,7 +22456,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -22517,7 +22517,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -22578,7 +22578,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -22639,7 +22639,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -22700,7 +22700,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -22761,7 +22761,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -22822,7 +22822,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -22883,7 +22883,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -22944,7 +22944,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -23005,7 +23005,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -23127,7 +23127,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -23188,7 +23188,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -23249,7 +23249,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -23310,7 +23310,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -23432,7 +23432,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -23615,7 +23615,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -23676,7 +23676,7 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -23737,7 +23737,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -23798,7 +23798,7 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -23859,7 +23859,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -23920,7 +23920,7 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -23981,7 +23981,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -24042,7 +24042,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -24103,7 +24103,7 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -24225,7 +24225,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -24286,7 +24286,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
@@ -24347,7 +24347,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -24408,7 +24408,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
@@ -24469,7 +24469,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -24530,7 +24530,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -24591,7 +24591,7 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
@@ -24652,7 +24652,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -24713,7 +24713,7 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
@@ -24774,7 +24774,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
@@ -24835,7 +24835,7 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
@@ -24957,7 +24957,7 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
@@ -25018,7 +25018,7 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
@@ -25079,7 +25079,7 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
@@ -25140,7 +25140,7 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -25262,7 +25262,7 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
@@ -25323,7 +25323,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -25384,7 +25384,7 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
@@ -25445,7 +25445,7 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
@@ -25506,7 +25506,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -25567,7 +25567,7 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
@@ -25628,7 +25628,7 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
@@ -25750,7 +25750,7 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
@@ -25811,7 +25811,7 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
@@ -25872,7 +25872,7 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
@@ -25933,7 +25933,7 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
@@ -25994,7 +25994,7 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
@@ -26055,7 +26055,7 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
@@ -26177,7 +26177,7 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
@@ -26238,7 +26238,7 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
@@ -26299,7 +26299,7 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
@@ -26421,7 +26421,7 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
@@ -26482,7 +26482,7 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
@@ -26543,7 +26543,7 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
@@ -26604,7 +26604,7 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
@@ -26665,7 +26665,7 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -26726,7 +26726,7 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
@@ -26787,7 +26787,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
@@ -26848,7 +26848,7 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
@@ -26909,7 +26909,7 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -27031,7 +27031,7 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
@@ -27092,7 +27092,7 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
@@ -27153,7 +27153,7 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
@@ -27214,7 +27214,7 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
@@ -27275,7 +27275,7 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
@@ -27336,7 +27336,7 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -27397,7 +27397,7 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -27458,7 +27458,7 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
@@ -27580,7 +27580,7 @@
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
@@ -27641,7 +27641,7 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -27702,7 +27702,7 @@
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
@@ -27763,7 +27763,7 @@
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
@@ -27824,7 +27824,7 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -27885,7 +27885,7 @@
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
@@ -27946,7 +27946,7 @@
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
@@ -28007,7 +28007,7 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -28068,7 +28068,7 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
@@ -28129,7 +28129,7 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -28190,7 +28190,7 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -28251,7 +28251,7 @@
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
@@ -28312,7 +28312,7 @@
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
@@ -28373,7 +28373,7 @@
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -28495,7 +28495,7 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -28556,7 +28556,7 @@
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
@@ -28617,7 +28617,7 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
@@ -28800,7 +28800,7 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -28861,7 +28861,7 @@
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
@@ -28922,7 +28922,7 @@
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -28983,7 +28983,7 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
@@ -29044,7 +29044,7 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
@@ -29105,7 +29105,7 @@
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
@@ -29166,7 +29166,7 @@
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
@@ -29227,7 +29227,7 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
@@ -29288,7 +29288,7 @@
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
@@ -29349,7 +29349,7 @@
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
@@ -29410,7 +29410,7 @@
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
@@ -29471,7 +29471,7 @@
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
@@ -29532,7 +29532,7 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
@@ -29593,7 +29593,7 @@
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
@@ -29654,7 +29654,7 @@
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
@@ -29715,7 +29715,7 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -29776,7 +29776,7 @@
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
@@ -29837,7 +29837,7 @@
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
@@ -29898,7 +29898,7 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -29959,7 +29959,7 @@
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
@@ -30020,7 +30020,7 @@
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
@@ -30081,7 +30081,7 @@
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I486" t="inlineStr">
@@ -30142,7 +30142,7 @@
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
@@ -30203,7 +30203,7 @@
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
@@ -30264,7 +30264,7 @@
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
@@ -30325,7 +30325,7 @@
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
@@ -30386,7 +30386,7 @@
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
@@ -30447,7 +30447,7 @@
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
@@ -30508,7 +30508,7 @@
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
@@ -30569,7 +30569,7 @@
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
@@ -30630,7 +30630,7 @@
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -30691,7 +30691,7 @@
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
@@ -30752,7 +30752,7 @@
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
@@ -30813,7 +30813,7 @@
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
@@ -30874,7 +30874,7 @@
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
@@ -30935,7 +30935,7 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
@@ -30996,7 +30996,7 @@
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
@@ -31057,7 +31057,7 @@
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
@@ -31118,7 +31118,7 @@
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
@@ -31179,7 +31179,7 @@
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -31240,7 +31240,7 @@
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
@@ -31301,7 +31301,7 @@
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
@@ -31362,7 +31362,7 @@
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
@@ -31423,7 +31423,7 @@
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
@@ -31484,7 +31484,7 @@
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
@@ -31545,7 +31545,7 @@
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -31667,7 +31667,7 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
@@ -31789,7 +31789,7 @@
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
@@ -31850,7 +31850,7 @@
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
@@ -31911,7 +31911,7 @@
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
@@ -31972,7 +31972,7 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -32033,7 +32033,7 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -32094,7 +32094,7 @@
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
@@ -32155,7 +32155,7 @@
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
@@ -32216,7 +32216,7 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
@@ -32277,7 +32277,7 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
@@ -32338,7 +32338,7 @@
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
@@ -32399,7 +32399,7 @@
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
@@ -32460,7 +32460,7 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -32521,7 +32521,7 @@
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
@@ -32582,7 +32582,7 @@
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
@@ -32643,7 +32643,7 @@
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
@@ -32765,7 +32765,7 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -32826,7 +32826,7 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -32887,7 +32887,7 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -32948,7 +32948,7 @@
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -33009,7 +33009,7 @@
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
@@ -33070,7 +33070,7 @@
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -33131,7 +33131,7 @@
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -33192,7 +33192,7 @@
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -33253,7 +33253,7 @@
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
@@ -33314,7 +33314,7 @@
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
@@ -33436,7 +33436,7 @@
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -33497,7 +33497,7 @@
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
@@ -33558,7 +33558,7 @@
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -33619,7 +33619,7 @@
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
@@ -33680,7 +33680,7 @@
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
@@ -33741,7 +33741,7 @@
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
@@ -33802,7 +33802,7 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -33863,7 +33863,7 @@
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -33924,7 +33924,7 @@
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
@@ -33985,7 +33985,7 @@
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
@@ -34107,7 +34107,7 @@
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
@@ -34168,7 +34168,7 @@
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
@@ -34229,7 +34229,7 @@
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
@@ -34290,7 +34290,7 @@
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
@@ -34351,7 +34351,7 @@
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
@@ -34412,7 +34412,7 @@
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
@@ -34473,7 +34473,7 @@
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
@@ -34534,7 +34534,7 @@
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -34595,7 +34595,7 @@
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
@@ -34656,7 +34656,7 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
@@ -34778,7 +34778,7 @@
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
@@ -34839,7 +34839,7 @@
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
@@ -34900,7 +34900,7 @@
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
@@ -34961,7 +34961,7 @@
       </c>
       <c r="H566" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
@@ -35022,7 +35022,7 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -35083,7 +35083,7 @@
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
@@ -35144,7 +35144,7 @@
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
@@ -35205,7 +35205,7 @@
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
@@ -35266,7 +35266,7 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
@@ -35327,7 +35327,7 @@
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I572" t="inlineStr">
@@ -35388,7 +35388,7 @@
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
@@ -35449,7 +35449,7 @@
       </c>
       <c r="H574" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I574" t="inlineStr">
@@ -35510,7 +35510,7 @@
       </c>
       <c r="H575" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
@@ -35571,7 +35571,7 @@
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I576" t="inlineStr">
@@ -35632,7 +35632,7 @@
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I577" t="inlineStr">
@@ -35693,7 +35693,7 @@
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
@@ -35754,7 +35754,7 @@
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I579" t="inlineStr">
@@ -35815,7 +35815,7 @@
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I580" t="inlineStr">
@@ -35876,7 +35876,7 @@
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I581" t="inlineStr">
@@ -36059,7 +36059,7 @@
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
@@ -36120,7 +36120,7 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -36181,7 +36181,7 @@
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I586" t="inlineStr">
@@ -36242,7 +36242,7 @@
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I587" t="inlineStr">
@@ -36303,7 +36303,7 @@
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
@@ -36364,7 +36364,7 @@
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I589" t="inlineStr">
@@ -36425,7 +36425,7 @@
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I590" t="inlineStr">
@@ -36486,7 +36486,7 @@
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
@@ -36547,7 +36547,7 @@
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I592" t="inlineStr">
@@ -36608,7 +36608,7 @@
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I593" t="inlineStr">
@@ -36669,7 +36669,7 @@
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
@@ -36730,7 +36730,7 @@
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -36791,7 +36791,7 @@
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I596" t="inlineStr">
@@ -36852,7 +36852,7 @@
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I597" t="inlineStr">
@@ -36913,7 +36913,7 @@
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
@@ -36974,7 +36974,7 @@
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -37035,7 +37035,7 @@
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
@@ -37096,7 +37096,7 @@
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
@@ -37157,7 +37157,7 @@
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
@@ -37218,7 +37218,7 @@
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I603" t="inlineStr">
@@ -37279,7 +37279,7 @@
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
@@ -37340,7 +37340,7 @@
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I605" t="inlineStr">
@@ -37401,7 +37401,7 @@
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I606" t="inlineStr">
@@ -37462,7 +37462,7 @@
       </c>
       <c r="H607" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I607" t="inlineStr">
@@ -37523,7 +37523,7 @@
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">
@@ -37584,7 +37584,7 @@
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
@@ -37645,7 +37645,7 @@
       </c>
       <c r="H610" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I610" t="inlineStr">
@@ -37767,7 +37767,7 @@
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I612" t="inlineStr">
@@ -37828,7 +37828,7 @@
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I613" t="inlineStr">
@@ -37889,7 +37889,7 @@
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I614" t="inlineStr">
@@ -37950,7 +37950,7 @@
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
@@ -38011,7 +38011,7 @@
       </c>
       <c r="H616" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I616" t="inlineStr">
@@ -38072,7 +38072,7 @@
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I617" t="inlineStr">
@@ -38133,7 +38133,7 @@
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I618" t="inlineStr">
@@ -38194,7 +38194,7 @@
       </c>
       <c r="H619" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I619" t="inlineStr">
@@ -38255,7 +38255,7 @@
       </c>
       <c r="H620" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I620" t="inlineStr">
@@ -38316,7 +38316,7 @@
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I621" t="inlineStr">
@@ -38377,7 +38377,7 @@
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I622" t="inlineStr">
@@ -38438,7 +38438,7 @@
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I623" t="inlineStr">
@@ -38499,7 +38499,7 @@
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I624" t="inlineStr">
@@ -38560,7 +38560,7 @@
       </c>
       <c r="H625" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I625" t="inlineStr">
@@ -38621,7 +38621,7 @@
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I626" t="inlineStr">
@@ -38682,7 +38682,7 @@
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I627" t="inlineStr">
@@ -38743,7 +38743,7 @@
       </c>
       <c r="H628" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I628" t="inlineStr">
@@ -38804,7 +38804,7 @@
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I629" t="inlineStr">
@@ -38865,7 +38865,7 @@
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I630" t="inlineStr">
@@ -38926,7 +38926,7 @@
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I631" t="inlineStr">
@@ -38987,7 +38987,7 @@
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I632" t="inlineStr">
@@ -39048,7 +39048,7 @@
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I633" t="inlineStr">
@@ -39109,7 +39109,7 @@
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I634" t="inlineStr">
@@ -39170,7 +39170,7 @@
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I635" t="inlineStr">
@@ -39231,7 +39231,7 @@
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I636" t="inlineStr">
@@ -39292,7 +39292,7 @@
       </c>
       <c r="H637" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I637" t="inlineStr">
@@ -39353,7 +39353,7 @@
       </c>
       <c r="H638" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I638" t="inlineStr">
@@ -39414,7 +39414,7 @@
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I639" t="inlineStr">
@@ -39475,7 +39475,7 @@
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I640" t="inlineStr">
@@ -39536,7 +39536,7 @@
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I641" t="inlineStr">
@@ -39597,7 +39597,7 @@
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I642" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/oct-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/oct-2025.xlsx
@@ -37996,7 +37996,7 @@
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F616" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/oct-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/oct-2025.xlsx
@@ -562,7 +562,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1663,11 @@
           <t>77.883.083-3</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1728,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1793,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1858,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1984,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2049,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2114,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2179,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2305,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2370,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2435,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2500,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2565,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2630,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2695,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2760,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2825,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2951,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3016,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3203,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3268,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3333,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3398,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3463,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3589,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3654,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3719,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3784,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3849,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3975,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4040,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4105,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4231,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4357,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4422,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4487,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4552,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4617,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4743,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4808,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4873,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4938,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +5003,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5068,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5194,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5442,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5507,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5572,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5637,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5763,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5828,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5954,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6080,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6145,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6210,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6275,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6340,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6405,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6531,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6657,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6722,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6848,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6913,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +6978,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7043,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7108,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7173,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7238,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7303,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7368,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7433,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7498,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7563,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7689,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7754,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7819,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7884,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +7949,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +8014,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8079,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8144,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8209,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8274,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8339,11 @@
           <t>77.809.872-5</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8404,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8530,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8595,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8660,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8847,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9533,7 +9953,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9594,7 +10018,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9655,7 +10083,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9777,7 +10209,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9838,7 +10274,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9899,7 +10339,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9960,7 +10404,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10021,7 +10469,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10082,7 +10534,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10143,7 +10599,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10204,7 +10664,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10265,7 +10729,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10448,7 +10916,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10570,7 +11042,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10631,7 +11107,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10936,7 +11416,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10997,7 +11481,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11058,7 +11546,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11119,7 +11611,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11180,7 +11676,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11241,7 +11741,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11302,7 +11806,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11363,7 +11871,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11485,7 +11997,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11546,7 +12062,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11607,7 +12127,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11668,7 +12192,11 @@
           <t>76.559.762-5</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11729,7 +12257,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11790,7 +12322,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11851,7 +12387,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11912,7 +12452,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11973,7 +12517,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12095,7 +12643,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12156,7 +12708,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12217,7 +12773,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12278,7 +12838,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12461,7 +13025,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12522,7 +13090,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12583,7 +13155,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12766,7 +13342,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12827,7 +13407,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12949,7 +13533,11 @@
           <t>77.547.396-7</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13071,7 +13659,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13193,7 +13785,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13254,7 +13850,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13315,7 +13915,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13376,7 +13980,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13437,7 +14045,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13498,7 +14110,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13559,7 +14175,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13620,7 +14240,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13681,7 +14305,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13742,7 +14370,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13803,7 +14435,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13864,7 +14500,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13986,7 +14626,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14047,7 +14691,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14169,7 +14817,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14291,7 +14943,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14352,7 +15008,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14413,7 +15073,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14535,7 +15199,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14596,7 +15264,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14657,7 +15329,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14718,7 +15394,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14779,7 +15459,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14840,7 +15524,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14901,7 +15589,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15023,7 +15715,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15145,7 +15841,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15328,7 +16028,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15389,7 +16093,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15450,7 +16158,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15572,7 +16284,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15633,7 +16349,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15816,7 +16536,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15877,7 +16601,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15938,7 +16666,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15999,7 +16731,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16060,7 +16796,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16121,7 +16861,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16304,7 +17048,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16491,7 +17239,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16552,7 +17304,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16674,7 +17430,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16735,7 +17495,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16796,7 +17560,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16857,7 +17625,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17040,7 +17812,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17101,7 +17877,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17223,7 +18003,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17284,7 +18068,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17345,7 +18133,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17406,7 +18198,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17467,7 +18263,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17528,7 +18328,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17589,7 +18393,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17650,7 +18458,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17894,7 +18706,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17955,7 +18771,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18016,7 +18836,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18077,7 +18901,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18138,7 +18966,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18199,7 +19031,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18260,7 +19096,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18321,7 +19161,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18382,7 +19226,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18443,7 +19291,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18504,7 +19356,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18565,7 +19421,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18626,7 +19486,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18687,7 +19551,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18748,7 +19616,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18809,7 +19681,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18870,7 +19746,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18931,7 +19811,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18992,7 +19876,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19053,7 +19941,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19175,7 +20067,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19236,7 +20132,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19297,7 +20197,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19419,7 +20323,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19480,7 +20388,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19602,7 +20514,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19724,7 +20640,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19785,7 +20705,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19907,7 +20831,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20029,7 +20957,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20090,7 +21022,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20456,7 +21392,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20517,7 +21457,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20578,7 +21522,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20639,7 +21587,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20700,7 +21652,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20761,7 +21717,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20822,7 +21782,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20883,7 +21847,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20944,7 +21912,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21005,7 +21977,11 @@
           <t>77.883.083-3</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21066,7 +22042,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21188,7 +22168,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21310,7 +22294,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21371,7 +22359,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21432,7 +22424,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21493,7 +22489,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21554,7 +22554,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21615,7 +22619,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21676,7 +22684,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21737,7 +22749,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21798,7 +22814,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21859,7 +22879,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21920,7 +22944,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21981,7 +23009,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22042,7 +23074,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22103,7 +23139,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22164,7 +23204,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22408,7 +23452,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22469,7 +23517,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22591,7 +23643,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22713,7 +23769,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22774,7 +23834,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22835,7 +23899,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22896,7 +23964,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22957,7 +24029,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23018,7 +24094,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23079,7 +24159,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23140,7 +24224,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23201,7 +24289,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23384,7 +24476,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23445,7 +24541,11 @@
           <t>77.720.988-4</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23506,7 +24606,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23567,7 +24671,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23628,7 +24736,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23689,7 +24801,11 @@
           <t>77.399.254-1</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23750,7 +24866,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23811,7 +24931,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23872,7 +24996,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23933,7 +25061,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23994,7 +25126,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24055,7 +25191,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24116,7 +25256,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24177,7 +25321,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24238,7 +25386,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24299,7 +25451,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24421,7 +25577,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24482,7 +25642,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24543,7 +25707,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24604,7 +25772,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24665,7 +25837,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24787,7 +25963,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24848,7 +26028,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24909,7 +26093,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25031,7 +26219,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25092,7 +26284,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25214,7 +26410,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25275,7 +26475,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25336,7 +26540,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25397,7 +26605,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25519,7 +26731,11 @@
           <t>78.091.613-3</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25580,7 +26796,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25641,7 +26861,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25702,7 +26926,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25824,7 +27052,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25946,7 +27178,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26007,7 +27243,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26068,7 +27308,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26129,7 +27373,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26190,7 +27438,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26251,7 +27503,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26312,7 +27568,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26373,7 +27633,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26434,7 +27698,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26495,7 +27763,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26556,7 +27828,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26617,7 +27893,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26678,7 +27958,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26739,7 +28023,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26800,7 +28088,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26861,7 +28153,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26922,7 +28218,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26983,7 +28283,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27044,7 +28348,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27105,7 +28413,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27166,7 +28478,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27227,7 +28543,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27349,7 +28669,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27410,7 +28734,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27471,7 +28799,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27532,7 +28864,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27654,7 +28990,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27715,7 +29055,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27776,7 +29120,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27837,7 +29185,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27898,7 +29250,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28081,7 +29437,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28142,7 +29502,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28203,7 +29567,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28264,7 +29632,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28325,7 +29697,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28386,7 +29762,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28447,7 +29827,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28508,7 +29892,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28569,7 +29957,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28630,7 +30022,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28691,7 +30087,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28752,7 +30152,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28813,7 +30217,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28874,7 +30282,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28996,7 +30408,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29057,7 +30473,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29118,7 +30538,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29179,7 +30603,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29240,7 +30668,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29301,7 +30733,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29423,7 +30859,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29484,7 +30924,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29545,7 +30989,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29606,7 +31054,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29667,7 +31119,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29728,7 +31184,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29789,7 +31249,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L481" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29850,7 +31314,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L482" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29972,7 +31440,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30033,7 +31505,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30094,7 +31570,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30155,7 +31635,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30216,7 +31700,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30277,7 +31765,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30338,7 +31830,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30399,7 +31895,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30582,7 +32082,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30765,7 +32269,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30887,7 +32395,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30948,7 +32460,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31009,7 +32525,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31314,7 +32834,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31375,7 +32899,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31497,7 +33025,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31558,7 +33090,11 @@
           <t>78.091.613-3</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L510" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31741,7 +33277,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31802,7 +33342,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31985,7 +33529,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32107,7 +33655,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32229,7 +33781,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L521" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32290,7 +33846,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32351,7 +33911,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32412,7 +33976,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K524" t="inlineStr"/>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L524" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32473,7 +34041,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32595,7 +34167,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32656,7 +34232,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L528" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32717,7 +34297,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L529" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32778,7 +34362,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32839,7 +34427,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L531" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32900,7 +34492,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K532" t="inlineStr"/>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L532" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32961,7 +34557,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33022,7 +34622,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33144,7 +34748,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr"/>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L536" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33205,7 +34813,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33266,7 +34878,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L538" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33327,7 +34943,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K539" t="inlineStr"/>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L539" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33388,7 +35008,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K540" t="inlineStr"/>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L540" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33449,7 +35073,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33693,7 +35321,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33754,7 +35386,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33815,7 +35451,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr"/>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L547" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33937,7 +35577,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K549" t="inlineStr"/>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L549" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33998,7 +35642,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K550" t="inlineStr"/>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L550" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34181,7 +35829,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K553" t="inlineStr"/>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L553" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34242,7 +35894,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K554" t="inlineStr"/>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L554" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34425,7 +36081,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34486,7 +36146,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K558" t="inlineStr"/>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L558" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34547,7 +36211,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34669,7 +36337,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34730,7 +36402,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K562" t="inlineStr"/>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L562" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34913,7 +36589,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K565" t="inlineStr"/>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L565" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34974,7 +36654,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K566" t="inlineStr"/>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L566" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35035,7 +36719,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr"/>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L567" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35096,7 +36784,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35157,7 +36849,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K569" t="inlineStr"/>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L569" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35218,7 +36914,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L570" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35340,7 +37040,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K572" t="inlineStr"/>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L572" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35401,7 +37105,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr"/>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L573" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35462,7 +37170,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L574" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35523,7 +37235,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K575" t="inlineStr"/>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L575" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35584,7 +37300,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35645,7 +37365,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L577" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35767,7 +37491,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K579" t="inlineStr"/>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L579" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35828,7 +37556,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr"/>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L580" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35889,7 +37621,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr"/>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L581" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35950,7 +37686,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K582" t="inlineStr"/>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L582" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36011,7 +37751,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K583" t="inlineStr"/>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L583" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36072,7 +37816,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L584" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36133,7 +37881,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K585" t="inlineStr"/>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L585" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36194,7 +37946,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K586" t="inlineStr"/>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L586" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36255,7 +38011,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K587" t="inlineStr"/>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L587" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36316,7 +38076,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L588" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36377,7 +38141,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36438,7 +38206,11 @@
           <t>76.559.762-5</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L590" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36499,7 +38271,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L591" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36560,7 +38336,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K592" t="inlineStr"/>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L592" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36621,7 +38401,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K593" t="inlineStr"/>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L593" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36682,7 +38466,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K594" t="inlineStr"/>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L594" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36804,7 +38592,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K596" t="inlineStr"/>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L596" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36865,7 +38657,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L597" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36926,7 +38722,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K598" t="inlineStr"/>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L598" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37048,7 +38848,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K600" t="inlineStr"/>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L600" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37109,7 +38913,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr"/>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L601" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37231,7 +39039,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L603" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37414,7 +39226,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K606" t="inlineStr"/>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L606" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37536,7 +39352,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K608" t="inlineStr"/>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L608" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37597,7 +39417,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K609" t="inlineStr"/>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L609" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37658,7 +39482,11 @@
           <t>76.559.762-5</t>
         </is>
       </c>
-      <c r="K610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L610" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37902,7 +39730,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K614" t="inlineStr"/>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L614" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38024,7 +39856,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K616" t="inlineStr"/>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L616" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38146,7 +39982,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38207,7 +40047,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K619" t="inlineStr"/>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L619" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38268,7 +40112,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K620" t="inlineStr"/>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L620" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38390,7 +40238,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K622" t="inlineStr"/>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L622" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38451,7 +40303,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K623" t="inlineStr"/>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L623" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38573,7 +40429,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr"/>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L625" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38695,7 +40555,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K627" t="inlineStr"/>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L627" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38756,7 +40620,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K628" t="inlineStr"/>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L628" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38817,7 +40685,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K629" t="inlineStr"/>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L629" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38878,7 +40750,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K630" t="inlineStr"/>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L630" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38939,7 +40815,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K631" t="inlineStr"/>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L631" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39000,7 +40880,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K632" t="inlineStr"/>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L632" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39061,7 +40945,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr"/>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L633" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39122,7 +41010,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K634" t="inlineStr"/>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L634" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39244,7 +41136,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K636" t="inlineStr"/>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L636" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39305,7 +41201,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K637" t="inlineStr"/>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L637" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39366,7 +41266,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K638" t="inlineStr"/>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L638" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39427,7 +41331,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K639" t="inlineStr"/>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L639" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39488,7 +41396,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K640" t="inlineStr"/>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L640" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39549,7 +41461,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K641" t="inlineStr"/>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L641" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39610,7 +41526,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K642" t="inlineStr"/>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L642" t="inlineStr">
         <is>
           <t>USD</t>
